--- a/data/performance/daily/signal_list_2026-06-11.xlsx
+++ b/data/performance/daily/signal_list_2026-06-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-11.xlsx
+++ b/data/performance/daily/signal_list_2026-06-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-11.xlsx
+++ b/data/performance/daily/signal_list_2026-06-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -686,15 +707,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -728,15 +754,20 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>1.83</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>17.07</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -879,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -889,9 +935,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,7 +968,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -946,15 +993,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -986,17 +1038,22 @@
       <c r="G5" s="4" t="n">
         <v>-7.59</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1028,17 +1085,22 @@
       <c r="G6" s="4" t="n">
         <v>-5.45</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,17 +1132,22 @@
       <c r="G7" s="4" t="n">
         <v>14.61</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1112,17 +1179,22 @@
       <c r="G8" s="4" t="n">
         <v>-7.14</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1154,17 +1226,22 @@
       <c r="G9" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G10" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G11" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G12" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1324,15 +1416,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G14" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1408,15 +1510,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,15 +1557,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G17" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1534,15 +1651,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1574,17 +1696,22 @@
       <c r="G19" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1618,15 +1745,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1660,15 +1792,20 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1702,15 +1839,20 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1742,17 +1884,22 @@
       <c r="G23" s="4" t="n">
         <v>1.87</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G24" s="4" t="n">
         <v>2.58</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,17 +1978,22 @@
       <c r="G25" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1870,15 +2027,20 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1910,17 +2072,22 @@
       <c r="G27" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1954,15 +2121,20 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1994,17 +2166,22 @@
       <c r="G29" s="4" t="n">
         <v>-10.83</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2038,15 +2215,20 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-11.xlsx
+++ b/data/performance/daily/signal_list_2026-06-11.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1490</v>
       </c>
       <c r="D5" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E5" t="n">
         <v>1485</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1505</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-0.34</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>5975</v>
       </c>
       <c r="D6" t="n">
-        <v>6000</v>
+        <v>5975</v>
       </c>
       <c r="E6" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.42</v>
+      <c r="F6" t="n">
+        <v>6000</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>0.42</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>795</v>
       </c>
       <c r="D7" t="n">
+        <v>795</v>
+      </c>
+      <c r="E7" t="n">
         <v>790</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>800</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1915</v>
       </c>
       <c r="D8" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E8" t="n">
         <v>1890</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1955</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.31</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>630</v>
       </c>
       <c r="D9" t="n">
+        <v>635</v>
+      </c>
+      <c r="E9" t="n">
         <v>605</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>645</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>2.38</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-3.97</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>8200</v>
       </c>
       <c r="D10" t="n">
-        <v>8350</v>
+        <v>8150</v>
       </c>
       <c r="E10" t="n">
         <v>8350</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>1.83</v>
+      <c r="F10" t="n">
+        <v>8350</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1.83</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>1.83</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>580</v>
       </c>
       <c r="D11" t="n">
+        <v>580</v>
+      </c>
+      <c r="E11" t="n">
         <v>555</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>580</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1025</v>
       </c>
       <c r="D12" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E12" t="n">
         <v>1200</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1280</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>24.88</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>17.07</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -925,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -933,12 +963,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,45 +999,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1027,33 +1063,36 @@
         <v>790</v>
       </c>
       <c r="D5" t="n">
+        <v>760</v>
+      </c>
+      <c r="E5" t="n">
         <v>730</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>780</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-7.59</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>110</v>
       </c>
       <c r="D6" t="n">
+        <v>109</v>
+      </c>
+      <c r="E6" t="n">
         <v>104</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>110</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-5.45</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>89</v>
       </c>
       <c r="D7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" t="n">
         <v>102</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>117</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>31.46</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>14.61</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>2660</v>
       </c>
       <c r="D8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E8" t="n">
         <v>2470</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2650</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-7.14</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>3590</v>
       </c>
       <c r="D9" t="n">
+        <v>3620</v>
+      </c>
+      <c r="E9" t="n">
         <v>3600</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>3870</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>7.8</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>21500</v>
       </c>
       <c r="D10" t="n">
+        <v>20500</v>
+      </c>
+      <c r="E10" t="n">
         <v>23500</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>24500</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>478</v>
       </c>
       <c r="D11" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E11" t="n">
         <v>480</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.42</v>
+      <c r="F11" t="n">
+        <v>480</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>0.42</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>123</v>
       </c>
       <c r="D12" t="n">
+        <v>125</v>
+      </c>
+      <c r="E12" t="n">
         <v>153</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>155</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>26.02</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>1915</v>
       </c>
       <c r="D13" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E13" t="n">
         <v>1890</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1955</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.31</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>1200</v>
       </c>
       <c r="D14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E14" t="n">
         <v>1205</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1210</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>165</v>
       </c>
       <c r="D15" t="n">
+        <v>165</v>
+      </c>
+      <c r="E15" t="n">
         <v>164</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>167</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.61</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>535</v>
       </c>
       <c r="D16" t="n">
+        <v>550</v>
+      </c>
+      <c r="E16" t="n">
         <v>462</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>550</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>2.8</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-13.64</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>350</v>
       </c>
       <c r="D17" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E17" t="n">
         <v>360</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>2.86</v>
+      <c r="F17" t="n">
+        <v>360</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H17" s="4" t="n">
+        <v>2.86</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>595</v>
       </c>
       <c r="D18" t="n">
+        <v>595</v>
+      </c>
+      <c r="E18" t="n">
         <v>570</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>610</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2.52</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>580</v>
       </c>
       <c r="D19" t="n">
+        <v>580</v>
+      </c>
+      <c r="E19" t="n">
         <v>555</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>580</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>62</v>
       </c>
       <c r="D20" t="n">
+        <v>62</v>
+      </c>
+      <c r="E20" t="n">
         <v>57</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>65</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>4.84</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-8.06</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>126</v>
       </c>
       <c r="D21" t="n">
+        <v>125</v>
+      </c>
+      <c r="E21" t="n">
         <v>122</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>128</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-3.17</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>344</v>
       </c>
       <c r="D22" t="n">
+        <v>338</v>
+      </c>
+      <c r="E22" t="n">
         <v>320</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>346</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-6.98</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>214</v>
       </c>
       <c r="D23" t="n">
+        <v>214</v>
+      </c>
+      <c r="E23" t="n">
         <v>218</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>224</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>4.67</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>1.87</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>310</v>
       </c>
       <c r="D24" t="n">
+        <v>312</v>
+      </c>
+      <c r="E24" t="n">
         <v>318</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>322</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>2.58</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>140</v>
       </c>
       <c r="D25" t="n">
+        <v>140</v>
+      </c>
+      <c r="E25" t="n">
         <v>150</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>172</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>22.86</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>350</v>
       </c>
       <c r="D26" t="n">
+        <v>370</v>
+      </c>
+      <c r="E26" t="n">
         <v>338</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>370</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-3.43</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>85</v>
       </c>
       <c r="D27" t="n">
+        <v>89</v>
+      </c>
+      <c r="E27" t="n">
         <v>86</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>94</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>10.59</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>870</v>
       </c>
       <c r="D28" t="n">
+        <v>900</v>
+      </c>
+      <c r="E28" t="n">
         <v>850</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>900</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>3.45</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-2.3</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>240</v>
       </c>
       <c r="D29" t="n">
+        <v>236</v>
+      </c>
+      <c r="E29" t="n">
         <v>214</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>236</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-10.83</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>100</v>
       </c>
       <c r="D30" t="n">
+        <v>101</v>
+      </c>
+      <c r="E30" t="n">
         <v>91</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>105</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
